--- a/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
+++ b/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
@@ -2965,7 +2965,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -3054,11 +3054,7 @@
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -3078,11 +3074,7 @@
         </is>
       </c>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
@@ -3106,11 +3098,7 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -3267,11 +3255,7 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
       <c r="G10" s="23"/>
@@ -3282,16 +3266,11 @@
         </is>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -3357,7 +3336,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⊏
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>
@@ -3437,23 +3416,15 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
       <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⊏
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
+++ b/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
@@ -2965,7 +2965,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -3336,7 +3336,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⊏
 南</t>
         </is>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⊏
 南</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
+++ b/sheets/조재수대금교본/검수/그 겨울의 찻집.xlsx
@@ -2914,26 +2914,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="50.63" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="75.27" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="75.27" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="75.27" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="75.27" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="75.27" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="75.27" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="75.27" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3247,7 +3247,7 @@
       <c r="N9" s="21"/>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="75.27" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="75.27" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="75.27" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="75.27" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="75.27" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3436,6 +3436,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="79"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>